--- a/incident database/AI Incident DB Analysis.xlsx
+++ b/incident database/AI Incident DB Analysis.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10309"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haoyug1/research/ethics_developer_interview/replication-package/incident database/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D444F0-A3F6-9E49-9D97-1759D397EA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59AB03F-A837-5A4B-9B64-E675F012E104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3400" yWindow="22360" windowWidth="30240" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5485,7 +5480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5498,12 +5493,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5828,7 +5817,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -5840,10 +5829,10 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="1" t="s">
         <v>1793</v>
       </c>
     </row>
@@ -5857,10 +5846,10 @@
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="1" t="s">
         <v>1794</v>
       </c>
     </row>
@@ -5874,10 +5863,10 @@
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="1" t="s">
         <v>1774</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="1" t="s">
         <v>1795</v>
       </c>
     </row>
@@ -5891,10 +5880,10 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="1" t="s">
         <v>1796</v>
       </c>
     </row>
@@ -5908,10 +5897,10 @@
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="1" t="s">
         <v>1797</v>
       </c>
     </row>
@@ -5925,10 +5914,10 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>1798</v>
       </c>
     </row>
@@ -5942,10 +5931,10 @@
       <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>1799</v>
       </c>
     </row>
@@ -5959,10 +5948,10 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="1" t="s">
         <v>1800</v>
       </c>
     </row>
